--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -97,11 +97,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,13 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -131,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -146,13 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -674,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -765,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -856,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -1948,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -2949,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -3950,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -4951,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -5952,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -6953,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -7954,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -8955,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9683,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9865,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -9956,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -10957,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11503,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11594,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11685,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -11958,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12595,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12868,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -12959,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13414,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13505,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13687,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13778,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -13960,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14142,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14324,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14597,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -14961,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15234,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15598,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -15962,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16144,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16235,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16508,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16690,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16781,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -16963,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17509,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17600,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17691,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17782,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -17964,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18055,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18146,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18419,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18601,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18874,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -18965,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19056,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19147,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19238,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19329,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19420,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19602,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -19966,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20057,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20421,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20512,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20785,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -20967,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21058,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21149,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21240,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21331,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21422,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21513,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21604,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21695,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21877,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -21968,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22059,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22150,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22241,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22423,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22514,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22605,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22696,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22787,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22878,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -22969,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23242,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23424,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23515,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23606,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -23970,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24152,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24243,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24516,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24607,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24698,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24789,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24880,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -24971,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25062,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25153,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25244,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25335,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25426,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25517,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25699,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25790,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -25972,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26063,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26154,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26245,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26336,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26518,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26609,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26700,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26791,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26882,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -26973,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27064,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27155,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27246,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27337,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27428,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27519,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27610,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27701,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27792,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27883,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -27974,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28156,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28247,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28338,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28429,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28520,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28611,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28702,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28793,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28884,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -28975,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29066,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29157,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29248,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29339,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29430,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29521,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29612,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29703,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29885,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -29976,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30067,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30249,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30340,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30431,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30613,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30704,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30795,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30886,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31068,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31159,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31250,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31341,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31432,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31523,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31614,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31705,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31796,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31887,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -31978,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32069,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32160,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32251,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32342,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32433,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32524,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32615,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32706,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32797,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32888,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -32979,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33070,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33161,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33252,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33343,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33434,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33525,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33616,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33707,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33798,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33889,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -33980,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34071,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34162,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34253,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34344,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34435,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34526,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34617,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34708,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34799,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34890,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -34981,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35072,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35163,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35254,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35345,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35436,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35527,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35618,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35709,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35800,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35891,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -35982,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36073,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36164,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36255,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36346,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36437,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36528,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36619,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36710,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36801,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36892,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -36983,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37074,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37165,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37256,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37347,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37438,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37529,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37620,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37711,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37802,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37893,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -37984,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38075,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38166,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38257,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38439,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38530,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38621,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38712,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38803,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38894,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -38985,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39076,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39167,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39258,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39440,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39531,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39622,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39713,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39804,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39895,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -39986,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40077,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40168,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40259,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40350,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40441,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40532,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40623,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40714,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40805,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40896,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -40987,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41078,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41169,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41260,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41351,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41442,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41533,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41624,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41715,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41806,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41897,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -41988,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42079,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42170,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42261,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42352,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42443,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42534,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42625,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42716,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42807,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42898,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -42989,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43080,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43171,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43262,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43353,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43444,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43535,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43626,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43717,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43808,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43899,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -43990,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44081,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44172,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44263,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44354,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44445,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44536,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44627,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44718,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44809,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44900,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -44991,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45082,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45173,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45264,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45355,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45446,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45537,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45628,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45719,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45810,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45901,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -45992,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46083,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46174,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46265,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46356,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46447,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46538,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46629,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46720,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46811,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46902,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -46993,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47084,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47175,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47266,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47357,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47448,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47539,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47630,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47721,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47812,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47903,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -47994,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48085,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48176,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48267,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48358,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48449,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48540,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48631,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48722,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48813,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48904,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -48995,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49086,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49177,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49268,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49359,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49450,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49541,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49632,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49723,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49814,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49905,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -49996,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50087,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50178,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50269,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50360,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50451,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50542,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50633,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50724,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50815,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50906,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -50997,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51088,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51179,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51270,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51361,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51452,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51543,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51634,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51725,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51816,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51907,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -51998,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52089,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52180,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52271,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52362,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52453,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52544,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52635,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52726,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52817,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52908,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -52999,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53090,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53181,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53272,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53363,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53454,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53545,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53636,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53727,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53818,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -53909,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54000,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54091,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54182,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54273,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54364,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54455,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54546,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54637,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54728,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54819,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -54910,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55001,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55092,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55183,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55274,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55365,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55456,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55547,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55638,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55729,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55820,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -55911,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56002,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56093,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56184,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56275,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56366,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56457,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56548,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56639,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56730,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56821,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -56912,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57003,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57094,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57185,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57276,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57367,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57458,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57549,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57640,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57731,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57822,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -57913,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58004,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58095,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58186,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58277,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58368,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58459,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58550,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58641,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58732,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58823,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -58914,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59005,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59096,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59187,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59278,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59369,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59460,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59551,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59683,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T10:52:06Z</t>
+          <t>2026-07-22T15:17:12Z</t>
         </is>
       </c>
     </row>
@@ -59763,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-22T10:52:06Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-22T15:17:12Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T15:17:12Z</t>
+          <t>2026-07-22T21:35:45Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-22T15:17:12Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-22T21:35:45Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:45Z</t>
+          <t>2026-07-23T21:35:03Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-22T21:35:45Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-23T21:35:03Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-23T21:35:03Z</t>
+          <t>2026-07-24T21:36:09Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-23T21:35:03Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-24T21:36:09Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:36:09Z</t>
+          <t>2026-07-25T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-24T21:36:09Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-25T21:23:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:58Z</t>
+          <t>2026-07-26T21:25:47Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-25T21:23:58Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-26T21:25:47Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:47Z</t>
+          <t>2026-07-27T21:37:28Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-26T21:25:47Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-27T21:37:28Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27T21:37:28Z</t>
+          <t>2026-07-28T21:37:48Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-27T21:37:28Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-28T21:37:48Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28T21:37:48Z</t>
+          <t>2026-07-29T21:26:22Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-28T21:37:48Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-29T21:26:22Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:26:22Z</t>
+          <t>2026-07-30T21:40:55Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-29T21:26:22Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-30T21:40:55Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30T21:40:55Z</t>
+          <t>2026-07-31T21:36:46Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-30T21:40:55Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-31T21:36:46Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:46Z</t>
+          <t>2026-08-01T21:23:57Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-07-31T21:36:46Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-08-01T21:23:57Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:57Z</t>
+          <t>2026-08-02T14:43:06Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-08-01T21:23:57Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-08-02T14:43:06Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @@
       </c>
       <c r="S456" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41692,7 +41692,7 @@
       </c>
       <c r="S457" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41783,7 +41783,7 @@
       </c>
       <c r="S458" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S459" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -41965,7 +41965,7 @@
       </c>
       <c r="S460" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42056,7 @@
       </c>
       <c r="S461" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42147,7 +42147,7 @@
       </c>
       <c r="S462" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42238,7 +42238,7 @@
       </c>
       <c r="S463" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42329,7 +42329,7 @@
       </c>
       <c r="S464" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42420,7 +42420,7 @@
       </c>
       <c r="S465" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42511,7 +42511,7 @@
       </c>
       <c r="S466" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="S467" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42693,7 +42693,7 @@
       </c>
       <c r="S468" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="S469" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42875,7 +42875,7 @@
       </c>
       <c r="S470" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -42966,7 +42966,7 @@
       </c>
       <c r="S471" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43057,7 +43057,7 @@
       </c>
       <c r="S472" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43148,7 +43148,7 @@
       </c>
       <c r="S473" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43239,7 +43239,7 @@
       </c>
       <c r="S474" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43330,7 +43330,7 @@
       </c>
       <c r="S475" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43421,7 +43421,7 @@
       </c>
       <c r="S476" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="S477" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="S478" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43694,7 @@
       </c>
       <c r="S479" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43785,7 +43785,7 @@
       </c>
       <c r="S480" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43876,7 +43876,7 @@
       </c>
       <c r="S481" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -43967,7 +43967,7 @@
       </c>
       <c r="S482" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="S483" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44149,7 +44149,7 @@
       </c>
       <c r="S484" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44240,7 +44240,7 @@
       </c>
       <c r="S485" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44331,7 +44331,7 @@
       </c>
       <c r="S486" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44422,7 +44422,7 @@
       </c>
       <c r="S487" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44513,7 @@
       </c>
       <c r="S488" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44604,7 +44604,7 @@
       </c>
       <c r="S489" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44695,7 +44695,7 @@
       </c>
       <c r="S490" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44786,7 +44786,7 @@
       </c>
       <c r="S491" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44877,7 +44877,7 @@
       </c>
       <c r="S492" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -44968,7 +44968,7 @@
       </c>
       <c r="S493" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45059,7 +45059,7 @@
       </c>
       <c r="S494" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45150,7 +45150,7 @@
       </c>
       <c r="S495" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S496" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45332,7 +45332,7 @@
       </c>
       <c r="S497" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45423,7 +45423,7 @@
       </c>
       <c r="S498" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45514,7 +45514,7 @@
       </c>
       <c r="S499" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45605,7 +45605,7 @@
       </c>
       <c r="S500" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45696,7 +45696,7 @@
       </c>
       <c r="S501" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45787,7 +45787,7 @@
       </c>
       <c r="S502" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="S503" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -45969,7 +45969,7 @@
       </c>
       <c r="S504" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46060,7 +46060,7 @@
       </c>
       <c r="S505" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46151,7 +46151,7 @@
       </c>
       <c r="S506" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46242,7 +46242,7 @@
       </c>
       <c r="S507" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46333,7 +46333,7 @@
       </c>
       <c r="S508" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46424,7 +46424,7 @@
       </c>
       <c r="S509" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="S510" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="S511" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46697,7 +46697,7 @@
       </c>
       <c r="S512" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S513" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S514" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -46970,7 +46970,7 @@
       </c>
       <c r="S515" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47061,7 +47061,7 @@
       </c>
       <c r="S516" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47152,7 +47152,7 @@
       </c>
       <c r="S517" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47243,7 +47243,7 @@
       </c>
       <c r="S518" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47334,7 +47334,7 @@
       </c>
       <c r="S519" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47425,7 +47425,7 @@
       </c>
       <c r="S520" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47516,7 +47516,7 @@
       </c>
       <c r="S521" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47607,7 +47607,7 @@
       </c>
       <c r="S522" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S523" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="S524" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47880,7 +47880,7 @@
       </c>
       <c r="S525" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -47971,7 +47971,7 @@
       </c>
       <c r="S526" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48062,7 +48062,7 @@
       </c>
       <c r="S527" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48153,7 +48153,7 @@
       </c>
       <c r="S528" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="S529" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="S530" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48426,7 +48426,7 @@
       </c>
       <c r="S531" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48517,7 +48517,7 @@
       </c>
       <c r="S532" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
       </c>
       <c r="S533" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48699,7 +48699,7 @@
       </c>
       <c r="S534" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48790,7 @@
       </c>
       <c r="S535" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48881,7 +48881,7 @@
       </c>
       <c r="S536" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -48972,7 +48972,7 @@
       </c>
       <c r="S537" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49063,7 +49063,7 @@
       </c>
       <c r="S538" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49154,7 +49154,7 @@
       </c>
       <c r="S539" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S540" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49336,7 +49336,7 @@
       </c>
       <c r="S541" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49427,7 +49427,7 @@
       </c>
       <c r="S542" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49518,7 +49518,7 @@
       </c>
       <c r="S543" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49609,7 +49609,7 @@
       </c>
       <c r="S544" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       </c>
       <c r="S545" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49791,7 +49791,7 @@
       </c>
       <c r="S546" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49882,7 +49882,7 @@
       </c>
       <c r="S547" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -49973,7 +49973,7 @@
       </c>
       <c r="S548" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50064,7 +50064,7 @@
       </c>
       <c r="S549" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50155,7 +50155,7 @@
       </c>
       <c r="S550" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50246,7 +50246,7 @@
       </c>
       <c r="S551" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="S552" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50428,7 +50428,7 @@
       </c>
       <c r="S553" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50519,7 +50519,7 @@
       </c>
       <c r="S554" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50610,7 +50610,7 @@
       </c>
       <c r="S555" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50701,7 +50701,7 @@
       </c>
       <c r="S556" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="S557" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50883,7 +50883,7 @@
       </c>
       <c r="S558" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -50974,7 +50974,7 @@
       </c>
       <c r="S559" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51065,7 +51065,7 @@
       </c>
       <c r="S560" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51156,7 +51156,7 @@
       </c>
       <c r="S561" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51247,7 +51247,7 @@
       </c>
       <c r="S562" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51338,7 +51338,7 @@
       </c>
       <c r="S563" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="S564" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51520,7 +51520,7 @@
       </c>
       <c r="S565" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="S566" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51702,7 +51702,7 @@
       </c>
       <c r="S567" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="S568" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S569" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="S570" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52066,7 +52066,7 @@
       </c>
       <c r="S571" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S572" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52248,7 +52248,7 @@
       </c>
       <c r="S573" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52339,7 +52339,7 @@
       </c>
       <c r="S574" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52430,7 +52430,7 @@
       </c>
       <c r="S575" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52521,7 +52521,7 @@
       </c>
       <c r="S576" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52612,7 +52612,7 @@
       </c>
       <c r="S577" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52703,7 +52703,7 @@
       </c>
       <c r="S578" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="S579" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52885,7 +52885,7 @@
       </c>
       <c r="S580" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -52976,7 +52976,7 @@
       </c>
       <c r="S581" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53067,7 +53067,7 @@
       </c>
       <c r="S582" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53158,7 +53158,7 @@
       </c>
       <c r="S583" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53249,7 +53249,7 @@
       </c>
       <c r="S584" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53340,7 +53340,7 @@
       </c>
       <c r="S585" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53431,7 +53431,7 @@
       </c>
       <c r="S586" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53522,7 +53522,7 @@
       </c>
       <c r="S587" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53613,7 +53613,7 @@
       </c>
       <c r="S588" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53704,7 +53704,7 @@
       </c>
       <c r="S589" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="S590" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53886,7 +53886,7 @@
       </c>
       <c r="S591" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -53977,7 +53977,7 @@
       </c>
       <c r="S592" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54068,7 +54068,7 @@
       </c>
       <c r="S593" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54159,7 +54159,7 @@
       </c>
       <c r="S594" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54250,7 +54250,7 @@
       </c>
       <c r="S595" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54341,7 +54341,7 @@
       </c>
       <c r="S596" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="S597" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54523,7 +54523,7 @@
       </c>
       <c r="S598" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54614,7 +54614,7 @@
       </c>
       <c r="S599" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54705,7 +54705,7 @@
       </c>
       <c r="S600" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54796,7 +54796,7 @@
       </c>
       <c r="S601" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54887,7 +54887,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55160,7 +55160,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55251,7 +55251,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55342,7 +55342,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55615,7 +55615,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55706,7 +55706,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55797,7 +55797,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55888,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56070,7 +56070,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56161,7 +56161,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56252,7 +56252,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56434,7 +56434,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56525,7 +56525,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56616,7 +56616,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56798,7 +56798,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56889,7 +56889,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -56980,7 +56980,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57071,7 +57071,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57162,7 +57162,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57253,7 +57253,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57344,7 +57344,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57435,7 +57435,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57526,7 +57526,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57617,7 +57617,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57708,7 +57708,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57799,7 +57799,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -57981,7 +57981,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58163,7 +58163,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58254,7 +58254,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58345,7 +58345,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58436,7 +58436,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58527,7 +58527,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58618,7 +58618,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59073,7 +59073,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59164,7 +59164,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59255,7 +59255,7 @@
       </c>
       <c r="S650" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59346,7 +59346,7 @@
       </c>
       <c r="S651" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59437,7 +59437,7 @@
       </c>
       <c r="S652" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="S653" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59619,7 +59619,7 @@
       </c>
       <c r="S654" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59751,7 +59751,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T14:43:06Z</t>
+          <t>2026-08-02T21:23:58Z</t>
         </is>
       </c>
     </row>
@@ -59831,7 +59831,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-08-02T14:43:06Z"}</t>
+          <t>{"dataset_id": "bcv_pib_sector_institucional_trimestral", "title": "Producto interno bruto por sector institucional trimestral", "table": "Variaciones porcentuales", "source_file": "5_2_1_si_trim.xlsx", "base": "2007", "price_type": "Precios constantes", "measure": "Variación porcentual interanual", "frequency": "Trimestral", "period": "2026-T1", "year": 2026, "quarter": 1, "classification": "Sector institucional", "component": "Impuestos netos sobre los productos", "value": 17.826324668500476, "unit": "Porcentaje", "status": "Preliminar", "source": "Banco Central de Venezuela", "source_url": "https://www.bcv.org.ve/sites/default/files/cuentas_macroeconomicas/5_2_1_si_trim.xlsx", "fetched_at": "2026-08-02T21:23:58Z"}</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_pib_sector_institucional_trimestral.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="S28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="S46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="S54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="S56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="S78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="S80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="S82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="S84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="S86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="S88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="S90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="S95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="S106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="S107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="S109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="S110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="S111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="S112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="S113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="S115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="S116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="S117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="S118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="S132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="S135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="S136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12845,7 +12845,7 @@
       </c>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="S143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="S146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="S147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="S152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="S154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="S155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="S156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14483,7 @@
       </c>
       <c r="S158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="S161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="S162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="S163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="S164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="S165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="S166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="S167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="S169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="S170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="S172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="S173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="S174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="S175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="S176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="S177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="S178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="S179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="S180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="S181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="S182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="S183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="S184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="S185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="S187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="S188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17304,7 @@
       </c>
       <c r="S189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="S190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="S192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="S193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="S194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="S195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17941,7 @@
       </c>
       <c r="S196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="S197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="S198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="S199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18396,7 @@
       </c>
       <c r="S201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18487,7 +18487,7 @@
       </c>
       <c r="S202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="S203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="S204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="S205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
       </c>
       <c r="S206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="S209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="S210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="S211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19397,7 +19397,7 @@
       </c>
       <c r="S212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="S213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="S214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="S215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="S216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="S217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
       </c>
       <c r="S218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="S220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20216,7 +20216,7 @@
       </c>
       <c r="S221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="S222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20398,7 +20398,7 @@
       </c>
       <c r="S223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="S224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="S225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
       </c>
       <c r="S226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="S227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="S228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="S229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="S230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="S231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="S232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="S233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="S234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="S236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="S238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="S239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="S240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22036,7 +22036,7 @@
       </c>
       <c r="S241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="S242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="S245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="S247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22673,7 @@
       </c>
       <c r="S248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="S249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="S250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="S252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="S253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23219,7 @@
       </c>
       <c r="S254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23310,7 @@
       </c>
       <c r="S255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="S256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23492,7 @@
       </c>
       <c r="S257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="S258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23765,7 +23765,7 @@
       </c>
       <c r="S260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="S263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="S264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="S266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24402,7 +24402,7 @@
       </c>
       <c r="S267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24493,7 +24493,7 @@
       </c>
       <c r="S268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24584,7 @@
       </c>
       <c r="S269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="S270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24766,7 +24766,7 @@
       </c>
       <c r="S271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24857,7 +24857,7 @@
       </c>
       <c r="S272" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="S273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25039,7 @@
       </c>
       <c r="S274" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="S275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25221,7 +25221,7 @@
       </c>
       <c r="S276" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="S277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="S278" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="S280" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="S281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="S282" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="S283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="S284" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="S285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="S286" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="S287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S288" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="S289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="S290" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26586,7 +26586,7 @@
       </c>
       <c r="S291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S292" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26768,7 +26768,7 @@
       </c>
       <c r="S293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="S294" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="S295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="S296" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="S297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="S298" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="S299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27405,7 +27405,7 @@
       </c>
       <c r="S300" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27496,7 @@
       </c>
       <c r="S301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="S302" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27678,7 @@
       </c>
       <c r="S303" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27769,7 +27769,7 @@
       </c>
       <c r="S304" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27860,7 +27860,7 @@
       </c>
       <c r="S305" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
       </c>
       <c r="S306" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28042,7 +28042,7 @@
       </c>
       <c r="S307" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="S308" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28224,7 +28224,7 @@
       </c>
       <c r="S309" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S310" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="S311" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S312" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="S313" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="S314" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28770,7 @@
       </c>
       <c r="S315" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28861,7 +28861,7 @@
       </c>
       <c r="S316" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S317" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29043,7 +29043,7 @@
       </c>
       <c r="S318" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="S319" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29225,7 +29225,7 @@
       </c>
       <c r="S320" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="S321" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="S322" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="S323" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="S324" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="S325" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="S326" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="S327" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="S328" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30044,7 +30044,7 @@
       </c>
       <c r="S329" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="S330" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="S331" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30317,7 +30317,7 @@
       </c>
       <c r="S332" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       </c>
       <c r="S333" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30499,7 @@
       </c>
       <c r="S334" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="S335" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30681,7 +30681,7 @@
       </c>
       <c r="S336" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30772,7 +30772,7 @@
       </c>
       <c r="S337" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30863,7 +30863,7 @@
       </c>
       <c r="S338" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="S339" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="S340" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="S341" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="S342" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31318,7 +31318,7 @@
       </c>
       <c r="S343" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31409,7 +31409,7 @@
       </c>
       <c r="S344" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31500,7 +31500,7 @@
       </c>
       <c r="S345" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="S346" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S347" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31773,7 +31773,7 @@
       </c>
       <c r="S348" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="S349" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="S350" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="S351" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32137,7 @@
       </c>
       <c r="S352" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32228,7 @@
       </c>
       <c r="S353" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S354" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32410,7 +32410,7 @@
       </c>
       <c r="S355" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32501,7 +32501,7 @@
       </c>
       <c r="S356" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="S357" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32683,7 +32683,7 @@
       </c>
       <c r="S358" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="S359" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="S360" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -32956,7 +32956,7 @@
       </c>
       <c r="S361" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="S362" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33138,7 +33138,7 @@
       </c>
       <c r="S363" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="S364" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33320,7 @@
       </c>
       <c r="S365" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33411,7 +33411,7 @@
       </c>
       <c r="S366" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S367" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33593,7 +33593,7 @@
       </c>
       <c r="S368" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="S369" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="S370" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33866,7 +33866,7 @@
       </c>
       <c r="S371" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -33957,7 +33957,7 @@
       </c>
       <c r="S372" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34048,7 +34048,7 @@
       </c>
       <c r="S373" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="S374" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34230,7 +34230,7 @@
       </c>
       <c r="S375" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34321,7 +34321,7 @@
       </c>
       <c r="S376" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34412,7 @@
       </c>
       <c r="S377" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="S378" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34594,7 +34594,7 @@
       </c>
       <c r="S379" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34685,7 +34685,7 @@
       </c>
       <c r="S380" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="S381" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="S382" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="S383" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S384" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35140,7 +35140,7 @@
       </c>
       <c r="S385" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35231,7 +35231,7 @@
       </c>
       <c r="S386" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35322,7 +35322,7 @@
       </c>
       <c r="S387" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S388" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35504,7 +35504,7 @@
       </c>
       <c r="S389" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35595,7 +35595,7 @@
       </c>
       <c r="S390" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35686,7 +35686,7 @@
       </c>
       <c r="S391" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35777,7 +35777,7 @@
       </c>
       <c r="S392" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35868,7 +35868,7 @@
       </c>
       <c r="S393" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -35959,7 +35959,7 @@
       </c>
       <c r="S394" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36050,7 +36050,7 @@
       </c>
       <c r="S395" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36141,7 @@
       </c>
       <c r="S396" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36232,7 +36232,7 @@
       </c>
       <c r="S397" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="S398" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36414,7 +36414,7 @@
       </c>
       <c r="S399" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36505,7 @@
       </c>
       <c r="S400" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36596,7 +36596,7 @@
       </c>
       <c r="S401" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36687,7 +36687,7 @@
       </c>
       <c r="S402" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36778,7 +36778,7 @@
       </c>
       <c r="S403" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="S404" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -36960,7 +36960,7 @@
       </c>
       <c r="S405" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37051,7 +37051,7 @@
       </c>
       <c r="S406" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37142,7 +37142,7 @@
       </c>
       <c r="S407" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="S408" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37324,7 +37324,7 @@
       </c>
       <c r="S409" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S410" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37506,7 +37506,7 @@
       </c>
       <c r="S411" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
       </c>
       <c r="S412" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37688,7 +37688,7 @@
       </c>
       <c r="S413" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37779,7 @@
       </c>
       <c r="S414" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37870,7 +37870,7 @@
       </c>
       <c r="S415" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -37961,7 +37961,7 @@
       </c>
       <c r="S416" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S417" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38143,7 +38143,7 @@
       </c>
       <c r="S418" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38234,7 +38234,7 @@
       </c>
       <c r="S419" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38325,7 +38325,7 @@
       </c>
       <c r="S420" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38416,7 +38416,7 @@
       </c>
       <c r="S421" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38507,7 +38507,7 @@
       </c>
       <c r="S422" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38598,7 +38598,7 @@
       </c>
       <c r="S423" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S424" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="S425" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38871,7 +38871,7 @@
       </c>
       <c r="S426" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -38962,7 +38962,7 @@
       </c>
       <c r="S427" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39053,7 +39053,7 @@
       </c>
       <c r="S428" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39144,7 @@
       </c>
       <c r="S429" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39235,7 +39235,7 @@
       </c>
       <c r="S430" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39326,7 +39326,7 @@
       </c>
       <c r="S431" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="S432" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39508,7 @@
       </c>
       <c r="S433" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39599,7 +39599,7 @@
       </c>
       <c r="S434" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S435" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39781,7 +39781,7 @@
       </c>
       <c r="S436" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
       </c>
       <c r="S437" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -39963,7 +39963,7 @@
       </c>
       <c r="S438" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40054,7 +40054,7 @@
       </c>
       <c r="S439" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="S440" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
       </c>
       <c r="S441" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40327,7 +40327,7 @@
       </c>
       <c r="S442" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40418,7 +40418,7 @@
       </c>
       <c r="S443" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40509,7 @@
       </c>
       <c r="S444" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40600,7 +40600,7 @@
       </c>
       <c r="S445" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="S446" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40782,7 +40782,7 @@
       </c>
       <c r="S447" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="S448" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -40964,7 +40964,7 @@
       </c>
       <c r="S449" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="S450" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -41146,7 +41146,7 @@
       </c>
       <c r="S451" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -41237,7 +41237,7 @@
       </c>
       <c r="S452" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S453" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41419,7 @@
       </c>
       <c r="S454" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41510,7 @@
       </c>
       <c r="S455" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:58Z</t>
+          <t>2026-08-03T21:38:53Z</t>
         </is>
       </c>
     </row>
@@ -41601,7 +41601,7 @